--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_01_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_01_22_Cau.xlsx
@@ -1321,7 +1321,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Sau bốn chunk đầy đủ vẫn còn 50 ký tự cần được phủ.</t>
+          <t>Với văn bản dài 1050 ký tự, chunk_size=250 và overlap=0 (step = 250): các chunk bắt đầu tại 0, 250, 500, 750 (4 chunk đầy đủ 250 ký tự = 1000 ký tự) và chunk thứ 5 bắt đầu tại vị trí 1000 chứa 50 ký tự còn lại. Do đó tạo ra 5 chunk, chunk cuối cùng có 50 ký tự.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_01_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_01_22_Cau.xlsx
@@ -674,10 +674,19 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một nguồn là kho tri thức; nguồn kia là trạng thái vận hành.
-Phân tích theo nguyên lý thiết kế: Một nguồn là kho tri thức; nguồn kia là trạng thái vận hành.</t>
+- [Phân loại &amp; Phương thức] (1.5 điểm): Xác định đúng RAG qua Vector DB cho chính sách tĩnh và Tool Calling/API cho số dư ngày phép thời gian thực.
+- [Bản chất dữ liệu &amp; Bất tương thích] (1.5 điểm): Phân tích sâu sắc sự khác biệt giữa tri thức phi cấu trúc (semantic search, trích dẫn) và dữ liệu trạng thái giao dịch (ACID, biến động cao, nguy cơ stale/hallucination khi index vào Vector DB).
+- [Trích dẫn &amp; Kiểm soát an toàn] (1.0 điểm): Nêu rõ cơ chế trích dẫn nguồn cho chính sách và xác thực danh tính bảo mật khi gọi API dữ liệu cá nhân.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn phương thức cung cấp dữ liệu cho từng nguồn:
+- Kho chính sách nội bộ (đổi hàng tháng): Sử dụng RAG Pipeline (Retrieval-Augmented Generation) với cơ sở dữ liệu vector (Vector DB). Tài liệu chính sách được trích xuất văn bản, phân đoạn (chunking), gắn metadata phân loại, sinh vector embeddings và lập chỉ mục. Khi người dùng truy vấn, hệ thống tìm kiếm các đoạn văn bản tương đồng cao nhất để đưa vào ngữ cảnh (context) kèm theo trích dẫn (citations) nguồn.
+- Số dư ngày phép còn lại (đổi thời gian thực theo từng giao dịch): Sử dụng cơ chế Gọi công cụ/Hàm (Tool Calling / Function Calling) kết nối trực tiếp đến API của hệ thống Quản lý nhân sự (HRIS / Core ERP Database) thông qua REST/gRPC endpoint có định danh người dùng và xác thực bảo mật.
+2. Lý do không thể dùng một phương thức duy nhất:
+Hai nguồn dữ liệu mang đặc tính và yêu cầu vận hành hoàn toàn trái ngược nhau. Chính sách nội bộ là tri thức phi cấu trúc, tĩnh trong chu kỳ dài (hàng tháng), đòi hỏi khả năng tìm kiếm ngữ nghĩa (semantic search) và trích dẫn nguyên văn điều khoản; nếu lưu trong bảng quan hệ cứng nhắc sẽ rất khó truy vấn tự nhiên. Ngược lại, số dư ngày phép là trạng thái vận hành thời gian thực (operational state), có tính biến động cao sau từng giao dịch và đòi hỏi tính toàn vẹn, chính xác tuyệt đối (ACID). Nếu đưa số dư ngày phép vào Vector DB, dữ liệu sẽ liên tục bị lỗi thời (stale), tốn chi phí re-indexing khổng lồ và đối mặt nguy cơ mô hình ngôn ngữ ảo giác (hallucination) về số ngày phép của nhân viên.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiến trúc ứng dụng AI doanh nghiệp, nguyên lý phân tách nguồn dữ liệu chỉ rõ sự khác biệt giữa 'Kho tri thức' (Knowledge Base) và 'Trạng thái vận hành thời gian thực' (Operational State). Kho tri thức phi cấu trúc phù hợp với RAG Pipeline vì dữ liệu ổn định và cần trích dẫn ngữ cảnh. Trạng thái vận hành đòi hỏi tính nhất quán giao dịch và dữ liệu mới nhất (freshness) từng giây, bắt buộc phải truy xuất qua Transactional API / Tool Calling để triệt tiêu nguy cơ stale index và ảo giác dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Documentation: 'Function Calling and Retrieval in Enterprise Architectures' (https://platform.openai.com/docs/guides/function-calling)</t>
         </is>
       </c>
     </row>
@@ -758,10 +767,18 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi trạng thái của ai/cái gì và nó thay đổi khi nào.
-Phân tích theo nguyên lý thiết kế: Hỏi trạng thái của ai/cái gì và nó thay đổi khi nào.</t>
+- [Phân loại chính xác 3 trường] (1.5 điểm): Phân loại đúng course_policy là tri thức tĩnh, seat_remaining là trạng thái vận hành thời gian thực, student_language là trạng thái phiên tạm thời.
+- [Bên phụ trách &amp; Nhịp cập nhật] (1.5 điểm): Xác định đúng chủ thể quản lý và nhịp độ thay đổi (học kỳ vs mili-giây giao dịch vs theo phiên).
+- [Phương thức truy cập kỹ thuật] (1.0 điểm): Đề xuất đúng kênh truy xuất: Vector DB RAG, Transactional API/SQL, và Session Context Injection.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại 3 trường dữ liệu:
+- `course_policy`: Dữ liệu tri thức tham chiếu / Chính sách đào tạo tĩnh (Static Reference Knowledge). Phụ trách bởi: Phòng Đào tạo (Academic Affairs). Nhịp cập nhật: Theo học kỳ hoặc chu kỳ năm học (tần suất rất thấp, hàng quý/năm). Cách truy cập phù hợp: Lưu trữ trong Document/Vector Store và truy xuất qua RAG với bộ lọc metadata.
+- `seat_remaining`: Dữ liệu trạng thái vận hành thời gian thực (Real-time Operational State). Phụ trách bởi: Hệ thống Quản lý Đào tạo / Đăng ký tín chỉ (Core SIS/LMS Database). Nhịp cập nhật: Theo từng giao dịch đặt/hủy chỗ của sinh viên (liên tục từng giây/mili-giây). Cách truy cập phù hợp: Gọi Tool/API trực tiếp đến dịch vụ kiểm tra chỗ hoặc truy vấn Redis/SQL với cơ chế khóa dữ liệu (locking/optimistic concurrency).
+- `student_language`: Dữ liệu trạng thái phiên tương tác người dùng (Session / Ephemeral Context State). Phụ trách bởi: Client / Web UI Frontend hoặc Session Manager. Nhịp cập nhật: Theo phiên làm việc hiện tại của người học (tồn tại tạm thời trong phiên chat, không lưu lâu dài). Cách truy cập phù hợp: Tiêm trực tiếp vào system prompt/ngữ cảnh hội thoại (Context Injection) trong payload gửi tới LLM.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hệ thống thông tin phân tán cần phân định ranh giới ngữ nghĩa truy cập dữ liệu (Access Semantics). Dữ liệu tham chiếu chu kỳ dài (course_policy) thuộc về hệ thống tri thức. Dữ liệu tài nguyên có thể cạnh tranh (seat_remaining) thuộc về hệ thống giao dịch thời gian thực. Trạng thái phiên cục bộ (student_language) thuộc về ngữ cảnh runtime, không làm biến đổi cơ sở dữ liệu backend.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Cloud Architecture Framework: 'Data Categorization and Access Semantics' (https://cloud.google.com/architecture/framework/system-design)</t>
         </is>
       </c>
     </row>
@@ -892,10 +909,19 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mục tiêu chỉ là so sánh nhóm chương trình và loại vấn đề, không phải theo dõi một người hay một ca hỗ trợ.
-Phân tích theo nguyên lý thiết kế: Mục tiêu chỉ là so sánh nhóm chương trình và loại vấn đề, không phải theo dõi một người hay một ca hỗ trợ.</t>
+- [Loại bỏ PII &amp; Dữ liệu nhạy cảm] (1.5 điểm): Chỉ rõ việc xóa advisor_name, student_email, support_case_id và giải thích căn cứ không cần liên kết ca/người học.
+- [Tái cấu trúc &amp; Làm giàu ngữ cảnh] (1.5 điểm): Thiết kế định dạng văn bản đưa vào embedder với tiền tố chương trình và danh mục vấn đề chuẩn hóa.
+- [Thiết kế Metadata lọc] (1.0 điểm): Chuyển program và issue_category thành trường metadata có cấu trúc để phục vụ pre-filtering/grouping.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế phép biến đổi dữ liệu trước khi tạo embeddings (Pre-embedding Transformation Pipeline):
+- Loại bỏ hoàn toàn dữ liệu định danh cá nhân (PII Elimination): Xóa bỏ các trường `advisor_name`, `student_email`, và `support_case_id`. Vì mục tiêu là so sánh các vấn đề phổ biến theo chương trình và không cần nối các ca hỗ trợ của cùng người học, các mã định danh này không mang giá trị ngữ nghĩa mà lại gây rủi ro rò rỉ dữ liệu nhạy cảm theo chuẩn GDPR/HIPAA và làm nhiễu không gian vector.
+- Chuẩn hóa và làm giàu ngữ cảnh (Contextual Normalization): Chuẩn hóa giá trị `program` (ví dụ: viết hoa thống nhất 'CS', 'AI', 'BA') và `issue_category` (chuyển thành taxonomy chuẩn hóa). Ghép tiền tố ngữ cảnh vào nội dung văn bản phản hồi, ví dụ: 'Chương trình: [program] | Chủ đề: [issue_category] | Nội dung phản hồi: [text]'.
+- Lưu trữ Metadata có cấu trúc: Đưa `program` và `issue_category` vào payload/metadata của vector để phục vụ việc lọc có điều kiện (filtered search / aggregate grouping) sau này.
+2. Lợi ích kỹ thuật: Việc loại bỏ PII giúp vector không gian chỉ tập trung vào ngữ nghĩa của vấn đề học thuật/hỗ trợ, tránh hiện tượng clustering theo tên cố vấn hay ID ca, đồng thời tuân thủ nghiêm ngặt nguyên tắc tối thiểu hóa dữ liệu (data minimization).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trước khi sinh vector embeddings, dữ liệu phải trải qua bước tiền xử lý nhằm bảo vệ quyền riêng tư và tối ưu hóa không gian biểu diễn. Dữ liệu PII vừa không có giá trị phân tích xu hướng vừa có thể bị trích xuất ngược qua các tấn công suy diễn (inversion attacks). Việc đưa thông tin phân loại vào metadata cho phép kết hợp giữa tìm kiếm tương đồng ngữ nghĩa và thống kê phân nhóm có cấu trúc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST Special Publication 800-122: 'Guide to Protecting the Confidentiality of Personally Identifiable Information (PII)' &amp; OWASP Top 10 for LLM: LLM06 Sensitive Information Disclosure</t>
         </is>
       </c>
     </row>
@@ -1026,10 +1052,23 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: PDF là định dạng bao chứa; kiểm tra xem có lớp chữ hay chỉ có ảnh.
-Phân tích theo nguyên lý thiết kế: PDF là định dạng bao chứa; kiểm tra xem có lớp chữ hay chỉ có ảnh.</t>
+- [Nhận diện PDF dạng ảnh] (1.0 điểm): Nêu rõ cách phát hiện khi MIME là application/pdf nhưng độ dài chuỗi ký tự bằng 0 hoặc dưới ngưỡng kèm đối tượng ảnh.
+- [Quy trình xử lý Fallback OCR] (1.0 điểm): Mô tả rõ quy trình chuyển đổi trang sang ảnh (render DPI) và áp dụng OCR engine.
+- [Phương pháp kiểm tra chất lượng] (1.0 điểm): Nêu các tiêu chí kiểm tra: độ tin cậy OCR, độ dài ký tự, kiểm thử tính toàn vẹn.
+- [Đặc tả nhật ký/Audit Log] (1.0 điểm): Định nghĩa cấu trúc log chi tiết ghi lại sự kiện fallback, lý do, và thông số thực thi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Cách nhận diện (Detection):
+Kiểm tra nội dung văn bản trích xuất từ các thư viện PDF thông thường (như PyPDF, PDFMiner, pypdfium2). Nếu MIME type là `application/pdf` nhưng tổng số ký tự trích xuất được (character count) bằng 0 hoặc tỷ lệ ký tự/trang dưới ngưỡng tối thiểu (ví dụ &lt; 20 ký tự/trang), đồng thời trang chứa đối tượng hình ảnh (XObject Image), hệ thống xác định đây là 'Scanned PDF' hoặc 'Image-only PDF'.
+2. Cách xử lý (Processing Strategy):
+Kích hoạt luồng xử lý dự phòng tự động (Fallback Routing): Chuyển hướng tài liệu sang bộ xử lý OCR chuyên dụng (như Tesseract, PaddleOCR, AWS Textract, hoặc Azure Document Intelligence). Chuyển từng trang PDF thành ảnh chất lượng cao (300 DPI), tiến hành tiền xử lý ảnh (khử nghiêng - deskew, khử nhiễu - denoise, tăng tương phản) và chạy OCR để trích xuất văn bản có tọa độ.
+3. Cách kiểm tra (Verification):
+So sánh kết quả đầu ra: Đo lường độ dài ký tự thu được, kiểm tra độ tin cậy của OCR (OCR confidence score &gt; 85%), và kiểm tra tính hợp lệ về mặt từ điển ngôn ngữ. Đối chiếu bằng mắt hoặc dùng phương pháp ngẫu nhiên kiểm tra trang có bảng/chữ.
+4. Nhật ký cần lưu giữ (Audit Logging):
+Ghi log chi tiết: `{file_id, file_name, mime_type, extractor_attempted: 'native_pdf', status: 'fallback_triggered', reason: 'empty_text_layer', fallback_extractor: 'tesseract_ocr', dpi: 300, extracted_char_count: 1420, avg_confidence: 0.92, processing_time_ms: 1250}`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+PDF là một định dạng đóng gói bao chứa (container format). Một tệp PDF có thể chứa văn bản số (digital native text) hoặc chỉ chứa ảnh quét (raster images). Hệ thống trích xuất tài liệu bắt buộc phải có cơ chế định tuyến linh hoạt (Extractor Routing): kiểm tra lớp văn bản trước, nếu rỗng thì kích hoạt pipeline OCR kèm nhật ký kiểm toán rõ ràng để phục vụ giám sát và gỡ lỗi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Unstructured Document Loaders and OCR Fallbacks' (https://python.langchain.com/docs/integrations/document_loaders/unstructured_file/)</t>
         </is>
       </c>
     </row>
@@ -1159,10 +1198,22 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Truy vấn phụ thuộc ngoại lệ thuộc mục nào.
-Phân tích theo nguyên lý thiết kế: Truy vấn phụ thuộc ngoại lệ thuộc mục nào.</t>
+- [Lựa chọn dạng biểu diễn] (1.0 điểm): Chọn Markdown có cấu trúc phân cấp và bảng Markdown.
+- [Phần giữ lại có căn cứ] (1.5 điểm): Nêu rõ việc giữ tiêu đề lồng nhau và bảng ngoại lệ gắn kèm mục cha để đảm bảo truy vấn đúng phạm vi.
+- [Phần loại bỏ triệt để] (1.0 điểm): Loại bỏ các thành phần điều hướng HTML, thẻ DOM rác, header/footer.
+- [Đánh giá chi phí biểu diễn] (0.5 điểm): Phân tích chi phí overhead token nhỏ nhưng đổi lại độ chính xác ngữ cảnh cao.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn dạng biểu diễn (Representation Format):
+Sử dụng định dạng Markdown có cấu trúc phân cấp (Hierarchical Markdown). Cấu trúc tiêu đề sử dụng các cấp `#`, `##`, `###` tương ứng với phân cấp chính sách. Bảng ngoại lệ được giữ nguyên dưới dạng bảng Markdown (Markdown Table) hoặc danh sách định dạng kèm ngữ cảnh rõ ràng.
+2. Phần cần giữ và phần cần bỏ:
+- Phần cần giữ: Giữ nguyên vẹn toàn bộ chuỗi tiêu đề tổ tiên (breadcrumbs/ancestor headings), nội dung điều khoản chính sách, và bảng ngoại lệ gắn liền với mục tương ứng. Mỗi bảng ngoại lệ phải được gắn kèm tiêu đề mục cha để bảo toàn phạm vi áp dụng.
+- Phần cần bỏ: Loại bỏ toàn bộ các thành phần điều hướng HTML (header, footer, navbar, sidebar, breadcrumb click elements, nút back-to-top, thẻ script, CSS style, div container vô nghĩa). Các thành phần này gây lãng phí token, làm loãng mật độ ngữ nghĩa và gây nhiễu cho mô hình embedding.
+3. Giải thích chi phí biểu diễn chấp nhận được:
+Việc giữ lại tiêu đề Markdown và bảng biểu chỉ làm tăng một lượng nhỏ overhead ký tự (khoảng 5-10% token so với văn bản thuần), nhưng mang lại giá trị sống còn: giúp retriever và LLM liên kết chính xác ngoại lệ với mục chính sách cha, ngăn chặn hoàn toàn lỗi gán nhầm ngoại lệ sang điều khoản khác.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống RAG, biểu diễn văn bản phải tối ưu hóa giữa tỷ lệ tín hiệu trên nhiễu (Signal-to-Noise Ratio) và chi phí token. Markdown là chuẩn biểu diễn tối ưu cho LLM vì cú pháp gọn nhẹ nhưng bảo toàn đầy đủ quan hệ thứ bậc của tiêu đề và quan hệ hàng-cột của bảng dữ liệu, trong khi việc loại bỏ nhiễu giao diện HTML giúp embedding vector tập trung vào nội dung tri thức cốt lõi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Markdown Node Parser &amp; Document Cleaners' (https://docs.llamaindex.ai/en/stable/module_guides/loading/documents_and_nodes/usage_documents/)</t>
         </is>
       </c>
     </row>
@@ -1239,10 +1290,32 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một trường dữ liệu chỉ hữu ích khi danh tính và tập giá trị nhất quán.
-Phân tích theo nguyên lý thiết kế: Một trường dữ liệu chỉ hữu ích khi danh tính và tập giá trị nhất quán.</t>
+- [Đặc tả Schema Contract] (1.5 điểm): Định nghĩa cấu trúc trường rõ ràng gồm department, language, semester với kiểu dữ liệu chuẩn.
+- [Tập giá trị cho phép] (1.5 điểm): Xác định tập giá trị đóng hoặc regex chuẩn cho từng trường (ISO ngôn ngữ, mã khoa, định dạng học kỳ).
+- [Hai quy tắc từ chối rõ ràng] (1.0 điểm): Đưa ra 2 quy tắc từ chối cụ thể khi thiếu trường, sai danh mục giá trị hoặc sai regex.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quy ước Metadata (Metadata Schema Contract):
+Mỗi bản ghi chunk chính sách khi nhập kho phải chứa trường metadata với định dạng JSON chuẩn hóa:
+```json
+{
+  "doc_id": "string (mã định danh duy nhất của chính sách)",
+  "department": "string (mã khoa/phòng ban)",
+  "language": "string (mã ngôn ngữ chuẩn ISO 639-1)",
+  "semester": "string (mã học kỳ chuẩn định dạng YYYY-S)",
+  "is_active": "boolean"
+}
+```
+2. Tập giá trị cho phép (Allowed Values / Value Constraints):
+- `department`: Thuộc danh mục mã khoa chuẩn hóa: `["CS", "EE", "BA", "LAW", "MED", "ALL"]` (viết hoa, không nhận biến thể tên dài).
+- `language`: Thuộc tập mã ISO 639-1 cho phép: `["vi", "en"]`.
+- `semester`: Chuỗi theo định dạng regex `^20\d{2}-(1|2|3|SUMMER)$` (ví dụ: `"2026-1"`, `"2026-2"`).
+3. Hai quy tắc từ chối bản ghi (Rejection / Quarantine Rules):
+- Quy tắc 1 (Thiếu trường bắt buộc hoặc giá trị ngoài danh mục): Bản ghi bị từ chối nhập kho nếu thiếu bất kỳ trường nào trong `{department, language, semester}` hoặc giá trị trường không thuộc tập giá trị cho phép (ví dụ `department="computer-science"` hoặc `language="vn"` thay vì `"vi"`).
+- Quy tắc 2 (Vi phạm định dạng thời gian/học kỳ): Bản ghi bị từ chối nếu `semester` không khớp biểu thức chính quy (ví dụ: `"Kỳ 1 năm 2026"` hoặc `"2026"`), để tránh làm gãy bộ lọc tiền truy vấn (pre-filter).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Metadata contract đóng vai trò là hàng rào bảo vệ tính toàn vẹn của chỉ mục vector (vector index integrity). Nếu metadata bị ô nhiễm bởi các giá trị tự do, bộ lọc metadata pre-filtering sẽ loại bỏ sai các tài liệu hợp lệ hoặc giữ lại các tài liệu rác. Một quy ước chặt chẽ với schema validation và chính sách cách ly (quarantine) ngay tại ingestion pipeline là điều kiện tiên quyết cho hệ thống RAG doanh nghiệp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pinecone Documentation: 'Metadata Filtering &amp; Schema Enforcement' (https://docs.pinecone.io/guides/data/filter-by-metadata)</t>
         </is>
       </c>
     </row>
@@ -1273,10 +1346,28 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cửa sổ tiến theo bước, không theo chunk_size.
-Phân tích theo nguyên lý thiết kế: Cửa sổ tiến theo bước, không theo chunk_size.</t>
+- [Tính đúng bước trượt] (1.0 điểm): Tính chính xác step = 400 - 100 = 300 ký tự.
+- [Liệt kê các vị trí bắt đầu] (1.0 điểm): Liệt kê chính xác 4 vị trí: 0, 300, 600, 900.
+- [Tính độ dài chunk cuối] (1.0 điểm): Tính chính xác độ dài chunk 4 là 150 ký tự (từ index 900 đến 1050).
+- [Xác định tổng số chunk] (1.0 điểm): Kết luận đúng tổng số chunk là 4.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính bước trượt (Step / Stride):
+`step = chunk_size - overlap = 400 - 100 = 300` ký tự.
+2. Xác định các vị trí bắt đầu (Start Positions) và phạm vi từng chunk:
+- Chunk 1: Bắt đầu tại index 0. Kết thúc tại: `min(0 + 400, 1050) = 400`. Phạm vi: [0, 400). Độ dài: 400 ký tự.
+- Chunk 2: Bắt đầu tại index `0 + 300 = 300`. Kết thúc tại: `min(300 + 400, 1050) = 700`. Phạm vi: [300, 700). Độ dài: 400 ký tự.
+- Chunk 3: Bắt đầu tại index `300 + 300 = 600`. Kết thúc tại: `min(600 + 400, 1050) = 1000`. Phạm vi: [600, 1000). Độ dài: 400 ký tự.
+- Chunk 4: Bắt đầu tại index `600 + 300 = 900`. Kết thúc tại: `min(900 + 400, 1050) = 1050`. Phạm vi: [900, 1050). Độ dài: `1050 - 900 = 150` ký tự.
+Vị trí bắt đầu tiếp theo nếu có sẽ là `900 + 300 = 1200 &gt;= 1050` (vượt quá độ dài văn bản), do đó dừng thuật toán.
+3. Tổng kết kết quả:
+- Bước trượt (Step): 300 ký tự.
+- Các vị trí bắt đầu: `[0, 300, 600, 900]`.
+- Độ dài chunk cuối cùng: 150 ký tự.
+- Tổng số chunk: 4 chunk.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong thuật toán phân đoạn cửa sổ trượt cố định (Fixed-size Sliding Window Chunking), cửa sổ dịch chuyển theo giá trị `step = chunk_size - overlap`, chứ không dịch chuyển theo `chunk_size`. Khi chỉ số bắt đầu cộng bước trượt đạt tới đoạn cuối của tài liệu, chunk cuối cùng sẽ được cắt ngắn tại độ dài thực tế của tài liệu (`total_length - start`), đảm bảo toàn bộ ký tự của tài liệu đều được bao phủ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'CharacterTextSplitter and Chunk Overlap Arithmetic' (https://python.langchain.com/docs/how_to/character_text_splitter/)</t>
         </is>
       </c>
     </row>
